--- a/etf_holdings/2026-09-17_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-17_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.61%364,000</t>
+          <t>9.11%364,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.61%</t>
+          <t>9.11%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.34%480,000</t>
+          <t>8.32%480,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.94%323,000</t>
+          <t>6.84%323,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.94%</t>
+          <t>6.84%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.34%1,720,000</t>
+          <t>6.23%1,720,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.34%</t>
+          <t>6.23%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.22%260,000</t>
+          <t>5.36%260,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.22%</t>
+          <t>5.36%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.09%665,000</t>
+          <t>5.15%665,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>5.15%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.60%378,000</t>
+          <t>4.64%378,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.60%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.29%1,127,000</t>
+          <t>4.12%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.13%212,000</t>
+          <t>3.83%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.80%54,300</t>
+          <t>3.82%54,300</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.06%920</t>
+          <t>-2.17%1800</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>-2.17%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>920</v>
+        <v>1800</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.75%1,030,000</t>
+          <t>3.67%529,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1030000</v>
+        <v>529000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.17%1800</t>
+          <t>-3.06%920</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-3.06%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1800</v>
+        <v>920</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.73%529,000</t>
+          <t>3.65%1,030,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>529000</v>
+        <v>1030000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.13%739,000</t>
+          <t>3.03%739,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.03%245,000</t>
+          <t>3.02%245,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:07</t>
+          <t>2026-09-17 21:39:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.82%120,000</t>
+          <t>2.84%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.12%271,000</t>
+          <t>2.18%271,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.97%1,200,000</t>
+          <t>1.99%1,200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.94%42,000</t>
+          <t>1.99%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.71%1320</t>
+          <t>+1.89%2425</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.71%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1320</v>
+        <v>2425</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.66%306,000</t>
+          <t>1.67%179,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>306000</v>
+        <v>179000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.89%2425</t>
+          <t>-6.71%1320</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.89%</t>
+          <t>-6.71%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2425</v>
+        <v>1320</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.63%179,000</t>
+          <t>1.56%306,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>179000</v>
+        <v>306000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.43%150,000</t>
+          <t>1.49%150,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.35%650,000</t>
+          <t>1.31%650,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.55%184</t>
+          <t>+3.87%147.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+3.87%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>184</v>
+        <v>147.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.98%1,400,000</t>
+          <t>1.01%1,778,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1400000</v>
+        <v>1778000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.87%147.5</t>
+          <t>+0.55%184</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>147.5</v>
+        <v>184</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.97%1,778,000</t>
+          <t>0.99%1,400,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1778000</v>
+        <v>1400000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.93%198,000</t>
+          <t>0.92%198,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.62%94,000</t>
+          <t>0.61%94,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.55%23,000</t>
+          <t>0.54%23,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:08</t>
+          <t>2026-09-17 21:39:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.50%250,000</t>
+          <t>0.51%250,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.40%110,000</t>
+          <t>0.39%110,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.34%400,000</t>
+          <t>0.35%400,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.26%95,000</t>
+          <t>0.27%95,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-17 17:22:10</t>
+          <t>2026-09-17 21:39:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-17_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-17_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:51</t>
+          <t>2026-09-17 21:47:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:52</t>
+          <t>2026-09-17 21:47:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-17 21:39:54</t>
+          <t>2026-09-17 21:47:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-17_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-17_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:21</t>
+          <t>2026-09-17 22:20:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:23</t>
+          <t>2026-09-17 22:20:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-17 21:47:24</t>
+          <t>2026-09-17 22:20:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
